--- a/filer/26864100_xlb.xlsx
+++ b/filer/26864100_xlb.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/26864100_xlb.xlsx
+++ b/filer/26864100_xlb.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_26864100" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_26864100" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_26864100" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_26864100" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +72,17 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -190,11 +203,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -230,6 +243,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -595,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -615,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Den uafhængige revisors erklær</t>
         </is>
       </c>
     </row>
@@ -629,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2976,35 +3010,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -3394,7 +3428,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3442,7 +3476,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3490,7 +3524,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B65" s="8">
@@ -3538,7 +3572,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3584,49 +3618,49 @@
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B67" s="11">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
         <f>'balance_raw_26864100'!$B$44</f>
         <v/>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="8">
         <f>'balance_raw_26864100'!$C$44</f>
         <v/>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="8">
         <f>'balance_raw_26864100'!$D$44</f>
         <v/>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="8">
         <f>'balance_raw_26864100'!$E$44</f>
         <v/>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="8">
         <f>'balance_raw_26864100'!$F$44</f>
         <v/>
       </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" s="12">
+      <c r="H67" s="9">
         <f>IFERROR(B67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="I67" s="12">
+      <c r="I67" s="9">
         <f>IFERROR(C67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="9">
         <f>IFERROR(D67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="9">
         <f>IFERROR(E67/$B$67*100,"")</f>
         <v/>
       </c>
-      <c r="L67" s="12">
+      <c r="L67" s="9">
         <f>IFERROR(F67/$B$67*100,"")</f>
         <v/>
       </c>
@@ -3634,7 +3668,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3682,7 +3716,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3730,7 +3764,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3778,7 +3812,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B71" s="8">
@@ -3826,7 +3860,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B72" s="5">
@@ -3874,7 +3908,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B73" s="8">
@@ -3920,823 +3954,725 @@
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B74" s="5">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B74" s="11">
         <f>'balance_raw_26864100'!$B$51</f>
         <v/>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="11">
         <f>'balance_raw_26864100'!$C$51</f>
         <v/>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="11">
         <f>'balance_raw_26864100'!$D$51</f>
         <v/>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="11">
         <f>'balance_raw_26864100'!$E$51</f>
         <v/>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="11">
         <f>'balance_raw_26864100'!$F$51</f>
         <v/>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="6">
+      <c r="H74" s="12">
         <f>IFERROR(B74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="I74" s="6">
+      <c r="I74" s="12">
         <f>IFERROR(C74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="J74" s="6">
+      <c r="J74" s="12">
         <f>IFERROR(D74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="12">
         <f>IFERROR(E74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="12">
         <f>IFERROR(F74/$B$74*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B75" s="8">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B75" s="11">
         <f>'balance_raw_26864100'!$B$52</f>
         <v/>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="11">
         <f>'balance_raw_26864100'!$C$52</f>
         <v/>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="11">
         <f>'balance_raw_26864100'!$D$52</f>
         <v/>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="11">
         <f>'balance_raw_26864100'!$E$52</f>
         <v/>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="11">
         <f>'balance_raw_26864100'!$F$52</f>
         <v/>
       </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="9">
+      <c r="H75" s="12">
         <f>IFERROR(B75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="12">
         <f>IFERROR(C75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="12">
         <f>IFERROR(D75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="K75" s="9">
+      <c r="K75" s="12">
         <f>IFERROR(E75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="L75" s="9">
+      <c r="L75" s="12">
         <f>IFERROR(F75/$B$75*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B76" s="5">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B76" s="11">
         <f>'balance_raw_26864100'!$B$53</f>
         <v/>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="11">
         <f>'balance_raw_26864100'!$C$53</f>
         <v/>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="11">
         <f>'balance_raw_26864100'!$D$53</f>
         <v/>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="11">
         <f>'balance_raw_26864100'!$E$53</f>
         <v/>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="11">
         <f>'balance_raw_26864100'!$F$53</f>
         <v/>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="6">
+      <c r="H76" s="12">
         <f>IFERROR(B76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="12">
         <f>IFERROR(C76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="J76" s="6">
+      <c r="J76" s="12">
         <f>IFERROR(D76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="12">
         <f>IFERROR(E76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="12">
         <f>IFERROR(F76/$B$76*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>'balance_raw_26864100'!$B$54</f>
-        <v/>
-      </c>
-      <c r="C77" s="8">
-        <f>'balance_raw_26864100'!$C$54</f>
-        <v/>
-      </c>
-      <c r="D77" s="8">
-        <f>'balance_raw_26864100'!$D$54</f>
-        <v/>
-      </c>
-      <c r="E77" s="8">
-        <f>'balance_raw_26864100'!$E$54</f>
-        <v/>
-      </c>
-      <c r="F77" s="8">
-        <f>'balance_raw_26864100'!$F$54</f>
-        <v/>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="9">
-        <f>IFERROR(B77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="I77" s="9">
-        <f>IFERROR(C77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="9">
-        <f>IFERROR(D77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="K77" s="9">
-        <f>IFERROR(E77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="L77" s="9">
-        <f>IFERROR(F77/$B$77*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B78" s="5">
-        <f>'balance_raw_26864100'!$B$55</f>
-        <v/>
-      </c>
-      <c r="C78" s="5">
-        <f>'balance_raw_26864100'!$C$55</f>
-        <v/>
-      </c>
-      <c r="D78" s="5">
-        <f>'balance_raw_26864100'!$D$55</f>
-        <v/>
-      </c>
-      <c r="E78" s="5">
-        <f>'balance_raw_26864100'!$E$55</f>
-        <v/>
-      </c>
-      <c r="F78" s="5">
-        <f>'balance_raw_26864100'!$F$55</f>
-        <v/>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="6">
-        <f>IFERROR(B78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="6">
-        <f>IFERROR(C78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="6">
-        <f>IFERROR(D78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="6">
-        <f>IFERROR(E78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="6">
-        <f>IFERROR(F78/$B$78*100,"")</f>
-        <v/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NØGLEOPLYSNINGER</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B79" s="11">
-        <f>'balance_raw_26864100'!$B$56</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>'balance_raw_26864100'!$C$56</f>
-        <v/>
-      </c>
-      <c r="D79" s="11">
-        <f>'balance_raw_26864100'!$D$56</f>
-        <v/>
-      </c>
-      <c r="E79" s="11">
-        <f>'balance_raw_26864100'!$E$56</f>
-        <v/>
-      </c>
-      <c r="F79" s="11">
-        <f>'balance_raw_26864100'!$F$56</f>
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>'res_raw_26864100'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C79" s="8">
+        <f>'res_raw_26864100'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D79" s="8">
+        <f>'res_raw_26864100'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E79" s="8">
+        <f>'res_raw_26864100'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F79" s="8">
+        <f>'res_raw_26864100'!$F$19</f>
         <v/>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="12">
+      <c r="H79" s="9">
         <f>IFERROR(B79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="I79" s="12">
+      <c r="I79" s="9">
         <f>IFERROR(C79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="J79" s="12">
+      <c r="J79" s="9">
         <f>IFERROR(D79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="K79" s="12">
+      <c r="K79" s="9">
         <f>IFERROR(E79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="L79" s="12">
+      <c r="L79" s="9">
         <f>IFERROR(F79/$B$79*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B80" s="11">
-        <f>'balance_raw_26864100'!$B$57</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>'balance_raw_26864100'!$C$57</f>
-        <v/>
-      </c>
-      <c r="D80" s="11">
-        <f>'balance_raw_26864100'!$D$57</f>
-        <v/>
-      </c>
-      <c r="E80" s="11">
-        <f>'balance_raw_26864100'!$E$57</f>
-        <v/>
-      </c>
-      <c r="F80" s="11">
-        <f>'balance_raw_26864100'!$F$57</f>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B80" s="5">
+        <f>'res_raw_26864100'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C80" s="5">
+        <f>'res_raw_26864100'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D80" s="5">
+        <f>'res_raw_26864100'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E80" s="5">
+        <f>'res_raw_26864100'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F80" s="5">
+        <f>'res_raw_26864100'!$F$20</f>
         <v/>
       </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="12">
+      <c r="H80" s="6">
         <f>IFERROR(B80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="I80" s="12">
+      <c r="I80" s="6">
         <f>IFERROR(C80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="J80" s="12">
+      <c r="J80" s="6">
         <f>IFERROR(D80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="K80" s="12">
+      <c r="K80" s="6">
         <f>IFERROR(E80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="L80" s="12">
+      <c r="L80" s="6">
         <f>IFERROR(F80/$B$80*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B81" s="11">
-        <f>'balance_raw_26864100'!$B$58</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>'balance_raw_26864100'!$C$58</f>
-        <v/>
-      </c>
-      <c r="D81" s="11">
-        <f>'balance_raw_26864100'!$D$58</f>
-        <v/>
-      </c>
-      <c r="E81" s="11">
-        <f>'balance_raw_26864100'!$E$58</f>
-        <v/>
-      </c>
-      <c r="F81" s="11">
-        <f>'balance_raw_26864100'!$F$58</f>
-        <v/>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" s="12">
-        <f>IFERROR(B81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="I81" s="12">
-        <f>IFERROR(C81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="12">
-        <f>IFERROR(D81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="K81" s="12">
-        <f>IFERROR(E81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="L81" s="12">
-        <f>IFERROR(F81/$B$81*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>NØGLEOPLYSNINGER</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C83" s="3" t="n">
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="C82" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="D82" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="E82" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B83" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$52*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B84" s="5">
-        <f>'res_raw_26864100'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C84" s="5">
-        <f>'res_raw_26864100'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D84" s="5">
-        <f>'res_raw_26864100'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E84" s="5">
-        <f>'res_raw_26864100'!$E$19</f>
-        <v/>
-      </c>
-      <c r="F84" s="5">
-        <f>'res_raw_26864100'!$F$19</f>
-        <v/>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" s="6">
-        <f>IFERROR(B84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="I84" s="6">
-        <f>IFERROR(C84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="J84" s="6">
-        <f>IFERROR(D84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="K84" s="6">
-        <f>IFERROR(E84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="L84" s="6">
-        <f>IFERROR(F84/$B$84*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>'res_raw_26864100'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C85" s="8">
-        <f>'res_raw_26864100'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D85" s="8">
-        <f>'res_raw_26864100'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E85" s="8">
-        <f>'res_raw_26864100'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F85" s="8">
-        <f>'res_raw_26864100'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" s="9">
-        <f>IFERROR(B85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="I85" s="9">
-        <f>IFERROR(C85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="J85" s="9">
-        <f>IFERROR(D85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="K85" s="9">
-        <f>IFERROR(E85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="L85" s="9">
-        <f>IFERROR(F85/$B$85*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>2024</v>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B85" s="13">
+        <f>IFERROR($B$4/$B$52,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="13">
+        <f>IFERROR($C$4/$C$52,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="13">
+        <f>IFERROR($D$4/$D$52,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="13">
+        <f>IFERROR($E$4/$E$52,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="13">
+        <f>IFERROR($F$4/$F$52,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B86" s="14">
+        <f>IFERROR($B$18/$B$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IFERROR($C$18/$C$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IFERROR($D$18/$D$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IFERROR($E$18/$E$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="14">
+        <f>IFERROR($F$18/$F$61*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B87" s="13">
+        <f>IFERROR($B$16/($B$76-$B$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="13">
+        <f>IFERROR($C$16/($C$76-$C$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="13">
+        <f>IFERROR($D$16/($D$76-$D$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="13">
+        <f>IFERROR($E$16/($E$76-$E$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="13">
+        <f>IFERROR($F$16/($F$76-$F$61)*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$52*100,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B88" s="14">
+        <f>IFERROR($B$61/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="14">
+        <f>IFERROR($C$61/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="14">
+        <f>IFERROR($D$61/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>IFERROR($E$61/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="14">
+        <f>IFERROR($F$61/$F$52*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B89" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B89" s="13">
+        <f>IFERROR(($B$76-$B$61)/$B$61,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>IFERROR(($C$76-$C$61)/$C$61,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="13">
+        <f>IFERROR(($D$76-$D$61)/$D$61,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="13">
+        <f>IFERROR(($E$76-$E$61)/$E$61,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="13">
+        <f>IFERROR(($F$76-$F$61)/$F$61,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B90" s="13">
-        <f>IFERROR($B$4/$B$52,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="13">
-        <f>IFERROR($C$4/$C$52,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="13">
-        <f>IFERROR($D$4/$D$52,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>IFERROR($E$4/$E$52,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="13">
-        <f>IFERROR($F$4/$F$52,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B90" s="14">
+        <f>IFERROR($B$51/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="14">
+        <f>IFERROR($C$51/$C$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IFERROR($D$51/$D$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IFERROR($E$51/$E$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="14">
+        <f>IFERROR($F$51/$F$74*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B91" s="14">
-        <f>IFERROR($B$18/$B$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="14">
-        <f>IFERROR($C$18/$C$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="14">
-        <f>IFERROR($D$18/$D$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="14">
-        <f>IFERROR($E$18/$E$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="14">
-        <f>IFERROR($F$18/$F$61*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B91" s="13">
+        <f>IFERROR(B83-B87,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="13">
+        <f>IFERROR(C83-C87,"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="13">
+        <f>IFERROR(D83-D87,"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="13">
+        <f>IFERROR(E83-E87,"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="13">
+        <f>IFERROR(F83-F87,"")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B92" s="13">
-        <f>IFERROR($B$16/($B$81-$B$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="13">
-        <f>IFERROR($C$16/($C$81-$C$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IFERROR($D$16/($D$81-$D$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IFERROR($E$16/($E$81-$E$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IFERROR($F$16/($F$81-$F$61)*100,"")</f>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B92" s="14">
+        <f>IFERROR(($B$76-$B$61)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="14">
+        <f>IFERROR(($C$76-$C$61)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="14">
+        <f>IFERROR(($D$76-$D$61)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="14">
+        <f>IFERROR(($E$76-$E$61)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="14">
+        <f>IFERROR(($F$76-$F$61)/$F$52*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B93" s="14">
-        <f>IFERROR($B$61/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C93" s="14">
-        <f>IFERROR($C$61/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="14">
-        <f>IFERROR($D$61/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="14">
-        <f>IFERROR($E$61/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="14">
-        <f>IFERROR($F$61/$F$52*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B94" s="13">
-        <f>IFERROR(($B$81-$B$61)/$B$61,"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="13">
-        <f>IFERROR(($C$81-$C$61)/$C$61,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="13">
-        <f>IFERROR(($D$81-$D$61)/$D$61,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>IFERROR(($E$81-$E$61)/$E$61,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="13">
-        <f>IFERROR(($F$81-$F$61)/$F$61,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B95" s="14">
-        <f>IFERROR($B$51/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="C95" s="14">
-        <f>IFERROR($C$51/$C$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="14">
-        <f>IFERROR($D$51/$D$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="14">
-        <f>IFERROR($E$51/$E$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="14">
-        <f>IFERROR($F$51/$F$79*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B96" s="13">
-        <f>IFERROR(B88-B92,"")</f>
-        <v/>
-      </c>
-      <c r="C96" s="13">
-        <f>IFERROR(C88-C92,"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="13">
-        <f>IFERROR(D88-D92,"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="13">
-        <f>IFERROR(E88-E92,"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="13">
-        <f>IFERROR(F88-F92,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B97" s="14">
-        <f>IFERROR(($B$81-$B$61)/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C97" s="14">
-        <f>IFERROR(($C$81-$C$61)/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="14">
-        <f>IFERROR(($D$81-$D$61)/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="14">
-        <f>IFERROR(($E$81-$E$61)/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F97" s="14">
-        <f>IFERROR(($F$81-$F$61)/$F$52*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B98" s="13">
-        <f>IFERROR($B$36/($B$61+$B$67)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C98" s="13">
-        <f>IFERROR($C$36/($C$61+$C$67)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="13">
-        <f>IFERROR($D$36/($D$61+$D$67)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="13">
-        <f>IFERROR($E$36/($E$61+$E$67)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="13">
-        <f>IFERROR($F$36/($F$61+$F$67)*100,"")</f>
+      <c r="B93" s="13">
+        <f>IFERROR($B$36/($B$61+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="13">
+        <f>IFERROR($C$36/($C$61+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>IFERROR($D$36/($D$61+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>IFERROR($E$36/($E$61+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="13">
+        <f>IFERROR($F$36/($F$61+0)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_26864100'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_26864100'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_26864100'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_26864100'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_26864100'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_26864100'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_26864100'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_26864100'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_26864100'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_26864100'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_26864100'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_26864100'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_26864100'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_26864100'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_26864100'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_26864100'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_26864100'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_26864100'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_26864100'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_26864100'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B100">
+        <f>IF(ABS(('pengestrom_raw_26864100'!$B$2+'pengestrom_raw_26864100'!$B$3+'pengestrom_raw_26864100'!$B$4)-'pengestrom_raw_26864100'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_26864100'!$B$2+'pengestrom_raw_26864100'!$B$3+'pengestrom_raw_26864100'!$B$4)-'pengestrom_raw_26864100'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>IF(ABS(('pengestrom_raw_26864100'!$C$2+'pengestrom_raw_26864100'!$C$3+'pengestrom_raw_26864100'!$C$4)-'pengestrom_raw_26864100'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_26864100'!$C$2+'pengestrom_raw_26864100'!$C$3+'pengestrom_raw_26864100'!$C$4)-'pengestrom_raw_26864100'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>IF(ABS(('pengestrom_raw_26864100'!$D$2+'pengestrom_raw_26864100'!$D$3+'pengestrom_raw_26864100'!$D$4)-'pengestrom_raw_26864100'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_26864100'!$D$2+'pengestrom_raw_26864100'!$D$3+'pengestrom_raw_26864100'!$D$4)-'pengestrom_raw_26864100'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>IF(ABS(('pengestrom_raw_26864100'!$E$2+'pengestrom_raw_26864100'!$E$3+'pengestrom_raw_26864100'!$E$4)-'pengestrom_raw_26864100'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_26864100'!$E$2+'pengestrom_raw_26864100'!$E$3+'pengestrom_raw_26864100'!$E$4)-'pengestrom_raw_26864100'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>IF(ABS(('pengestrom_raw_26864100'!$F$2+'pengestrom_raw_26864100'!$F$3+'pengestrom_raw_26864100'!$F$4)-'pengestrom_raw_26864100'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_26864100'!$F$2+'pengestrom_raw_26864100'!$F$3+'pengestrom_raw_26864100'!$F$4)-'pengestrom_raw_26864100'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4769,411 +4705,411 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>6053125</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>6566702</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>6386452</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>5453341</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>4816829</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>3808643</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>38440</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>40132</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>44261</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>43178</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>39836</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>39574</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>6024760</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>6541195</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>6363438</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>5434228</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>4783001</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>3783246</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>16175</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>15131</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>17347</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>15837</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>15141</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>15653</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>50630</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>50508</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>49928</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>46454</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>58523</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>49318</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>41282</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>40546</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>41309</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>41390</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>41252</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>40771</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>7477</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>7356</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>6077</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>4912</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>7110</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>7549</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>1871</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>2606</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>2542</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>152</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>10161</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>998</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>290</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>73</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1170</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>2432</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>1244</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>783</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>1595</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>693</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>159</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>152</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>-493</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-1522</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-628</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1011</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>2280</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>1378</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1084</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>1914</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>1163</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>12441</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>2194</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>232</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>388</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>151</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>118</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>202</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>268</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>1146</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>696</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>1763</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1045</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>12239</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>1926</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>68</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>64</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>62</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>840</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>252</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>71</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5188,7 +5124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5206,1049 +5142,995 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>9039</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>7365</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>4713</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>8452</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>16723</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>8326</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>9039</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>7365</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>4713</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>8452</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>16723</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>8326</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>3960</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>3650</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>3424</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>3124</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>2824</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>2524</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>178</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>678</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>503</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>237</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>68</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>4138</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>4328</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>3927</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>3361</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>2892</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>2549</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>322</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>332</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>342</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>128</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>128</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>6936</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>5723</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3511</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>3764</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>681</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>980</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>20113</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>17416</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>12151</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>15577</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>20296</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>11855</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n">
         <v>31370</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>17762</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>9789</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>33626</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>60771</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>53234</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>31370</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>17762</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>9789</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>834456</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>949366</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>888345</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>854293</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>879762</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>558050</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>162945</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>171274</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>135772</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>126462</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>148101</v>
       </c>
+      <c r="F22" s="17" t="n">
+        <v>36199</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>4064</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>2048</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>3184</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>6791</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>3654</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>2791</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n">
         <v>83</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>189</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>219</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n">
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n">
         <v>36</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>1010471</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>1122725</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>1027384</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>987735</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>1031772</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>597237</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n">
         <v>29812</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>30749</v>
       </c>
+      <c r="F28" s="17" t="n">
+        <v>30209</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>162059</v>
-      </c>
-      <c r="C29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>20535</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>38045</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>21909</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>34250</v>
       </c>
+      <c r="F29" s="17" t="n">
+        <v>98111</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>1206156</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>1204031</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>1118663</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>1070826</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>1114533</v>
       </c>
+      <c r="F30" s="17" t="n">
+        <v>735346</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>1226269</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>1221447</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>1130814</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>1086403</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>1134829</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>747201</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>975</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>850</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>825</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>750</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>675</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>625</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>-6428</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>3747</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>-1599</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>-415</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>1384</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>353590</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>225479</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>212547</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>210406</v>
       </c>
-      <c r="F36" s="16" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>5771</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>6467</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>8230</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>9275</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>10385</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>12311</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>370142</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>254628</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>239252</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>238516</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>250579</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>24348</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>1151</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>1050</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>820</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>648</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>585</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>511</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n">
+        <v>194461</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>3858</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>926408</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>845438</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>810904</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>845237</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>473415</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="C45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>804263</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>926408</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>845438</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>810904</v>
-      </c>
-      <c r="F49" s="16" t="n">
-        <v>845237</v>
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>38487</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>44579</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>35743</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>37744</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>53840</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>0</v>
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>589</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>520</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>554</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>5390</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>965769</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>890742</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>847239</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>883665</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>722342</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>166</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>136</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>130</v>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>965769</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>890742</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>847239</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>883665</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>722342</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>45987</v>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>38487</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>44579</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>35743</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>37744</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>702</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>589</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>520</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>851118</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>965769</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>890742</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>847239</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>883665</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>854976</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>965769</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>890742</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>847239</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>883665</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
-        <v>1226269</v>
-      </c>
-      <c r="C58" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>1221447</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>1130814</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>1086403</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>1134829</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>747201</v>
       </c>
     </row>
   </sheetData>
@@ -6257,6 +6139,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>-134820</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>18240</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>21683</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>26014</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>67678</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-4572</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-1735</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-36708</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-11489</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-2132</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-824</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-1975</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-5405</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6287,13 +6291,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6728,15 +6732,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_26864100'!$F$58-'balance_raw_26864100'!$F$38</f>
+        <f>'balance_raw_26864100'!$F$53-'balance_raw_26864100'!$F$38</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_26864100'!$E$58-'balance_raw_26864100'!$E$38</f>
+        <f>'balance_raw_26864100'!$E$53-'balance_raw_26864100'!$E$38</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_26864100'!$D$58-'balance_raw_26864100'!$D$38</f>
+        <f>'balance_raw_26864100'!$D$53-'balance_raw_26864100'!$D$38</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6842,15 +6846,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_26864100'!$F$56</f>
+        <f>'balance_raw_26864100'!$F$51</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_26864100'!$E$56</f>
+        <f>'balance_raw_26864100'!$E$51</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_26864100'!$D$56</f>
+        <f>'balance_raw_26864100'!$D$51</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -7007,7 +7011,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7125,7 +7129,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7301,7 +7305,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7358,15 +7362,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_26864100'!$F$58="","—",IF(ABS(B25-'balance_raw_26864100'!$F$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_26864100'!$F$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_26864100'!$F$53="","—",IF(ABS(B25-'balance_raw_26864100'!$F$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_26864100'!$F$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_26864100'!$E$58="","—",IF(ABS(C25-'balance_raw_26864100'!$E$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_26864100'!$E$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_26864100'!$E$53="","—",IF(ABS(C25-'balance_raw_26864100'!$E$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_26864100'!$E$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_26864100'!$D$58="","—",IF(ABS(D25-'balance_raw_26864100'!$D$58)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_26864100'!$D$58,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_26864100'!$D$53="","—",IF(ABS(D25-'balance_raw_26864100'!$D$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_26864100'!$D$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7477,4 +7481,141 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Dansk navn</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>XBRL feltnavn</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2021 t.kr.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2022 t.kr.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023 t.kr.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2024 t.kr.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2025 t.kr.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Forklaring</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ProceedsFromSalesOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ProceedsFromSalesOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n">
+        <v>30749</v>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>